--- a/raw/processedSamples/20260519_r12_CMH_USDA-blood_RT-QuIC.xlsx
+++ b/raw/processedSamples/20260519_r12_CMH_USDA-blood_RT-QuIC.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnpro\Desktop\RT-QuIC Data\Caylie\20260519_r12_CMH_USDA-blood_RT-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80951B8-03DA-485E-81BD-77E0E8C9040B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B273128-978A-4BBA-82BA-B3814BC83010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="1020" windowWidth="23730" windowHeight="13170" activeTab="2" xr2:uid="{523893DB-9DAA-4A15-94CC-8F610E0E5FCF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{523893DB-9DAA-4A15-94CC-8F610E0E5FCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Time 1 (0 h)" sheetId="2" r:id="rId1"/>
     <sheet name="Table All Data points" sheetId="1" r:id="rId2"/>
-    <sheet name="Curves" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -853,55 +852,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>227503</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB1DC213-1C7E-C486-4D78-DA5C78AB708B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="95250" y="57150"/>
-          <a:ext cx="12324253" cy="3724275"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1222,13 +1172,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:O45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="15" max="15" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>4</v>
+      </c>
+    </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
@@ -2071,37 +2026,37 @@
         <v>1000</v>
       </c>
       <c r="C38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="H38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="K38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="L38" s="12">
-        <v>100</v>
-      </c>
-      <c r="M38" s="13">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="M38" s="12">
+        <v>4</v>
       </c>
       <c r="O38" s="21"/>
     </row>
@@ -2112,38 +2067,38 @@
       <c r="B39" s="5">
         <v>1000</v>
       </c>
-      <c r="C39" s="14">
-        <v>100</v>
-      </c>
-      <c r="D39" s="14">
-        <v>100</v>
-      </c>
-      <c r="E39" s="14">
-        <v>100</v>
-      </c>
-      <c r="F39" s="14">
-        <v>100</v>
-      </c>
-      <c r="G39" s="14">
-        <v>100</v>
-      </c>
-      <c r="H39" s="14">
-        <v>100</v>
-      </c>
-      <c r="I39" s="14">
-        <v>100</v>
-      </c>
-      <c r="J39" s="14">
-        <v>100</v>
-      </c>
-      <c r="K39" s="14">
-        <v>100</v>
-      </c>
-      <c r="L39" s="14">
-        <v>100</v>
-      </c>
-      <c r="M39" s="15">
-        <v>100</v>
+      <c r="C39" s="12">
+        <v>4</v>
+      </c>
+      <c r="D39" s="12">
+        <v>4</v>
+      </c>
+      <c r="E39" s="12">
+        <v>4</v>
+      </c>
+      <c r="F39" s="12">
+        <v>4</v>
+      </c>
+      <c r="G39" s="12">
+        <v>4</v>
+      </c>
+      <c r="H39" s="12">
+        <v>4</v>
+      </c>
+      <c r="I39" s="12">
+        <v>4</v>
+      </c>
+      <c r="J39" s="12">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12">
+        <v>4</v>
+      </c>
+      <c r="L39" s="12">
+        <v>4</v>
+      </c>
+      <c r="M39" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -2153,38 +2108,38 @@
       <c r="B40" s="5">
         <v>1000</v>
       </c>
-      <c r="C40" s="14">
-        <v>100</v>
-      </c>
-      <c r="D40" s="14">
-        <v>100</v>
-      </c>
-      <c r="E40" s="14">
-        <v>100</v>
-      </c>
-      <c r="F40" s="14">
-        <v>100</v>
-      </c>
-      <c r="G40" s="14">
-        <v>100</v>
-      </c>
-      <c r="H40" s="14">
-        <v>100</v>
-      </c>
-      <c r="I40" s="14">
-        <v>100</v>
-      </c>
-      <c r="J40" s="14">
-        <v>100</v>
-      </c>
-      <c r="K40" s="14">
-        <v>100</v>
-      </c>
-      <c r="L40" s="14">
-        <v>100</v>
-      </c>
-      <c r="M40" s="15">
-        <v>100</v>
+      <c r="C40" s="12">
+        <v>4</v>
+      </c>
+      <c r="D40" s="12">
+        <v>4</v>
+      </c>
+      <c r="E40" s="12">
+        <v>4</v>
+      </c>
+      <c r="F40" s="12">
+        <v>4</v>
+      </c>
+      <c r="G40" s="12">
+        <v>4</v>
+      </c>
+      <c r="H40" s="12">
+        <v>4</v>
+      </c>
+      <c r="I40" s="12">
+        <v>4</v>
+      </c>
+      <c r="J40" s="12">
+        <v>4</v>
+      </c>
+      <c r="K40" s="12">
+        <v>4</v>
+      </c>
+      <c r="L40" s="12">
+        <v>4</v>
+      </c>
+      <c r="M40" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -2194,38 +2149,38 @@
       <c r="B41" s="5">
         <v>1000</v>
       </c>
-      <c r="C41" s="14">
-        <v>100</v>
-      </c>
-      <c r="D41" s="14">
-        <v>100</v>
-      </c>
-      <c r="E41" s="14">
-        <v>100</v>
-      </c>
-      <c r="F41" s="14">
-        <v>100</v>
-      </c>
-      <c r="G41" s="14">
-        <v>100</v>
-      </c>
-      <c r="H41" s="14">
-        <v>100</v>
-      </c>
-      <c r="I41" s="14">
-        <v>100</v>
-      </c>
-      <c r="J41" s="14">
-        <v>100</v>
-      </c>
-      <c r="K41" s="14">
-        <v>100</v>
-      </c>
-      <c r="L41" s="14">
-        <v>100</v>
-      </c>
-      <c r="M41" s="15">
-        <v>100</v>
+      <c r="C41" s="12">
+        <v>4</v>
+      </c>
+      <c r="D41" s="12">
+        <v>4</v>
+      </c>
+      <c r="E41" s="12">
+        <v>4</v>
+      </c>
+      <c r="F41" s="12">
+        <v>4</v>
+      </c>
+      <c r="G41" s="12">
+        <v>4</v>
+      </c>
+      <c r="H41" s="12">
+        <v>4</v>
+      </c>
+      <c r="I41" s="12">
+        <v>4</v>
+      </c>
+      <c r="J41" s="12">
+        <v>4</v>
+      </c>
+      <c r="K41" s="12">
+        <v>4</v>
+      </c>
+      <c r="L41" s="12">
+        <v>4</v>
+      </c>
+      <c r="M41" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2235,38 +2190,38 @@
       <c r="B42" s="5">
         <v>1000</v>
       </c>
-      <c r="C42" s="14">
-        <v>100</v>
-      </c>
-      <c r="D42" s="14">
-        <v>100</v>
-      </c>
-      <c r="E42" s="14">
-        <v>100</v>
-      </c>
-      <c r="F42" s="14">
-        <v>100</v>
-      </c>
-      <c r="G42" s="14">
-        <v>100</v>
-      </c>
-      <c r="H42" s="14">
-        <v>100</v>
-      </c>
-      <c r="I42" s="14">
-        <v>100</v>
-      </c>
-      <c r="J42" s="14">
-        <v>100</v>
-      </c>
-      <c r="K42" s="14">
-        <v>100</v>
-      </c>
-      <c r="L42" s="14">
-        <v>100</v>
-      </c>
-      <c r="M42" s="15">
-        <v>100</v>
+      <c r="C42" s="12">
+        <v>4</v>
+      </c>
+      <c r="D42" s="12">
+        <v>4</v>
+      </c>
+      <c r="E42" s="12">
+        <v>4</v>
+      </c>
+      <c r="F42" s="12">
+        <v>4</v>
+      </c>
+      <c r="G42" s="12">
+        <v>4</v>
+      </c>
+      <c r="H42" s="12">
+        <v>4</v>
+      </c>
+      <c r="I42" s="12">
+        <v>4</v>
+      </c>
+      <c r="J42" s="12">
+        <v>4</v>
+      </c>
+      <c r="K42" s="12">
+        <v>4</v>
+      </c>
+      <c r="L42" s="12">
+        <v>4</v>
+      </c>
+      <c r="M42" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2276,38 +2231,38 @@
       <c r="B43" s="5">
         <v>1000</v>
       </c>
-      <c r="C43" s="14">
-        <v>100</v>
-      </c>
-      <c r="D43" s="14">
-        <v>100</v>
-      </c>
-      <c r="E43" s="14">
-        <v>100</v>
-      </c>
-      <c r="F43" s="14">
-        <v>100</v>
-      </c>
-      <c r="G43" s="14">
-        <v>100</v>
-      </c>
-      <c r="H43" s="14">
-        <v>100</v>
-      </c>
-      <c r="I43" s="14">
-        <v>100</v>
-      </c>
-      <c r="J43" s="14">
-        <v>100</v>
-      </c>
-      <c r="K43" s="14">
-        <v>100</v>
-      </c>
-      <c r="L43" s="14">
-        <v>100</v>
-      </c>
-      <c r="M43" s="15">
-        <v>100</v>
+      <c r="C43" s="12">
+        <v>4</v>
+      </c>
+      <c r="D43" s="12">
+        <v>4</v>
+      </c>
+      <c r="E43" s="12">
+        <v>4</v>
+      </c>
+      <c r="F43" s="12">
+        <v>4</v>
+      </c>
+      <c r="G43" s="12">
+        <v>4</v>
+      </c>
+      <c r="H43" s="12">
+        <v>4</v>
+      </c>
+      <c r="I43" s="12">
+        <v>4</v>
+      </c>
+      <c r="J43" s="12">
+        <v>4</v>
+      </c>
+      <c r="K43" s="12">
+        <v>4</v>
+      </c>
+      <c r="L43" s="12">
+        <v>4</v>
+      </c>
+      <c r="M43" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2317,38 +2272,38 @@
       <c r="B44" s="5">
         <v>1000</v>
       </c>
-      <c r="C44" s="14">
-        <v>100</v>
-      </c>
-      <c r="D44" s="14">
-        <v>100</v>
-      </c>
-      <c r="E44" s="14">
-        <v>100</v>
-      </c>
-      <c r="F44" s="14">
-        <v>100</v>
-      </c>
-      <c r="G44" s="14">
-        <v>100</v>
-      </c>
-      <c r="H44" s="14">
-        <v>100</v>
-      </c>
-      <c r="I44" s="14">
-        <v>100</v>
-      </c>
-      <c r="J44" s="14">
-        <v>100</v>
-      </c>
-      <c r="K44" s="14">
-        <v>100</v>
-      </c>
-      <c r="L44" s="14">
-        <v>100</v>
-      </c>
-      <c r="M44" s="15">
-        <v>100</v>
+      <c r="C44" s="12">
+        <v>4</v>
+      </c>
+      <c r="D44" s="12">
+        <v>4</v>
+      </c>
+      <c r="E44" s="12">
+        <v>4</v>
+      </c>
+      <c r="F44" s="12">
+        <v>4</v>
+      </c>
+      <c r="G44" s="12">
+        <v>4</v>
+      </c>
+      <c r="H44" s="12">
+        <v>4</v>
+      </c>
+      <c r="I44" s="12">
+        <v>4</v>
+      </c>
+      <c r="J44" s="12">
+        <v>4</v>
+      </c>
+      <c r="K44" s="12">
+        <v>4</v>
+      </c>
+      <c r="L44" s="12">
+        <v>4</v>
+      </c>
+      <c r="M44" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -2358,38 +2313,38 @@
       <c r="B45" s="16">
         <v>1000</v>
       </c>
-      <c r="C45" s="17">
-        <v>100</v>
-      </c>
-      <c r="D45" s="17">
-        <v>100</v>
-      </c>
-      <c r="E45" s="17">
-        <v>100</v>
-      </c>
-      <c r="F45" s="17">
-        <v>100</v>
-      </c>
-      <c r="G45" s="17">
-        <v>100</v>
-      </c>
-      <c r="H45" s="17">
-        <v>100</v>
-      </c>
-      <c r="I45" s="17">
-        <v>100</v>
-      </c>
-      <c r="J45" s="17">
-        <v>100</v>
-      </c>
-      <c r="K45" s="17">
-        <v>100</v>
-      </c>
-      <c r="L45" s="17">
-        <v>100</v>
-      </c>
-      <c r="M45" s="18">
-        <v>100</v>
+      <c r="C45" s="12">
+        <v>4</v>
+      </c>
+      <c r="D45" s="12">
+        <v>4</v>
+      </c>
+      <c r="E45" s="12">
+        <v>4</v>
+      </c>
+      <c r="F45" s="12">
+        <v>4</v>
+      </c>
+      <c r="G45" s="12">
+        <v>4</v>
+      </c>
+      <c r="H45" s="12">
+        <v>4</v>
+      </c>
+      <c r="I45" s="12">
+        <v>4</v>
+      </c>
+      <c r="J45" s="12">
+        <v>4</v>
+      </c>
+      <c r="K45" s="12">
+        <v>4</v>
+      </c>
+      <c r="L45" s="12">
+        <v>4</v>
+      </c>
+      <c r="M45" s="12">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -89168,18 +89123,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C379C6A5-04F2-46C8-A66C-9D560038E5D9}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="47" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>